--- a/sources/jin_step9.xlsx
+++ b/sources/jin_step9.xlsx
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>f~N,d ~df+2 -</t>
+          <t>f~N,d~df+2 -</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">

--- a/sources/jin_step9.xlsx
+++ b/sources/jin_step9.xlsx
@@ -1001,6 +1001,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -1053,6 +1058,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -1110,6 +1120,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -1167,6 +1182,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -1224,6 +1244,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -1281,6 +1306,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -1348,6 +1378,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1410,6 +1445,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1470,6 +1510,11 @@
       <c r="V16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -11453,6 +11498,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -11500,6 +11550,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -11547,6 +11602,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -11594,6 +11654,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -11641,6 +11706,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -11688,6 +11758,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -11735,6 +11810,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -11782,6 +11862,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -11829,6 +11914,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -11874,6 +11964,11 @@
       <c r="T138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
